--- a/src/main/resources/ScanTestData.xlsx
+++ b/src/main/resources/ScanTestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation Setup\AST Automation\Automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF6D2CB-6CB7-43B6-887D-5F4BF21D1739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9181A05E-BC8A-4E17-A1DC-1F4DD2E430C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="170" windowWidth="19200" windowHeight="11110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScanSheet" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="91">
   <si>
     <t>ScenarioDescription</t>
   </si>
@@ -105,9 +105,6 @@
     <t>containers</t>
   </si>
   <si>
-    <t>SAST scan with valid application name</t>
-  </si>
-  <si>
     <t>`--application-name ""</t>
   </si>
   <si>
@@ -292,6 +289,24 @@
   </si>
   <si>
     <t>SAST scan with multipe Application in single command</t>
+  </si>
+  <si>
+    <t>`--iac-security-platforms terraform</t>
+  </si>
+  <si>
+    <t>`--iac-security-platforms</t>
+  </si>
+  <si>
+    <t>flag needs an argument: --iac-security-platforms</t>
+  </si>
+  <si>
+    <t>KICS scan with Platform set as terraform</t>
+  </si>
+  <si>
+    <t>KICS scan with empty Platform</t>
+  </si>
+  <si>
+    <t>`--iac-security-platforms Invalid_platform</t>
   </si>
 </sst>
 </file>
@@ -664,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.90625" customWidth="1"/>
@@ -696,12 +711,12 @@
         <v>11</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -722,13 +737,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -745,13 +760,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
@@ -808,11 +823,14 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
@@ -825,13 +843,19 @@
       <c r="G7" t="s">
         <v>15</v>
       </c>
+      <c r="H7" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>85</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
@@ -843,15 +867,15 @@
         <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -863,15 +887,15 @@
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
@@ -883,21 +907,15 @@
         <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
@@ -909,18 +927,18 @@
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>8</v>
+        <v>22</v>
+      </c>
+      <c r="H11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
@@ -933,20 +951,17 @@
       </c>
       <c r="G12" t="s">
         <v>8</v>
-      </c>
-      <c r="H12" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
         <v>9</v>
@@ -959,17 +974,20 @@
       </c>
       <c r="G13" t="s">
         <v>8</v>
+      </c>
+      <c r="H13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
@@ -982,20 +1000,17 @@
       </c>
       <c r="G14" t="s">
         <v>8</v>
-      </c>
-      <c r="H14" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>24</v>
+      <c r="C15" t="s">
+        <v>76</v>
       </c>
       <c r="D15" t="s">
         <v>9</v>
@@ -1008,17 +1023,20 @@
       </c>
       <c r="G15" t="s">
         <v>8</v>
+      </c>
+      <c r="H15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>79</v>
+      <c r="C16" t="s">
+        <v>75</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
@@ -1035,13 +1053,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
         <v>9</v>
@@ -1054,20 +1072,17 @@
       </c>
       <c r="G17" t="s">
         <v>8</v>
-      </c>
-      <c r="H17" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
         <v>9</v>
@@ -1082,18 +1097,18 @@
         <v>8</v>
       </c>
       <c r="H18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
       </c>
-      <c r="C19" t="s">
-        <v>50</v>
+      <c r="C19" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="D19" t="s">
         <v>9</v>
@@ -1106,17 +1121,20 @@
       </c>
       <c r="G19" t="s">
         <v>8</v>
+      </c>
+      <c r="H19" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
-      <c r="C20" t="s">
-        <v>51</v>
+      <c r="C20" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
@@ -1133,13 +1151,13 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
         <v>9</v>
@@ -1156,13 +1174,13 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
         <v>9</v>
@@ -1175,46 +1193,43 @@
       </c>
       <c r="G22" t="s">
         <v>8</v>
-      </c>
-      <c r="H22" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" t="s">
         <v>47</v>
-      </c>
-      <c r="B23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
         <v>9</v>
@@ -1229,41 +1244,44 @@
         <v>8</v>
       </c>
       <c r="H24" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" t="s">
         <v>56</v>
-      </c>
-      <c r="B25" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
         <v>9</v>
@@ -1276,20 +1294,17 @@
       </c>
       <c r="G26" t="s">
         <v>8</v>
-      </c>
-      <c r="H26" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D27" t="s">
         <v>9</v>
@@ -1298,21 +1313,24 @@
         <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="G27" t="s">
         <v>8</v>
+      </c>
+      <c r="H27" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
         <v>9</v>
@@ -1325,20 +1343,17 @@
       </c>
       <c r="G28" t="s">
         <v>8</v>
-      </c>
-      <c r="H28" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s">
         <v>9</v>
@@ -1353,18 +1368,18 @@
         <v>8</v>
       </c>
       <c r="H29" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
@@ -1377,32 +1392,81 @@
       </c>
       <c r="G30" t="s">
         <v>8</v>
+      </c>
+      <c r="H30" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" t="s">
         <v>74</v>
       </c>
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>73</v>
       </c>
-      <c r="D31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" t="s">
-        <v>8</v>
-      </c>
-      <c r="H31" t="s">
-        <v>75</v>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1417,6 +1481,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="53.7265625" customWidth="1"/>
+    <col min="2" max="2" width="14.6328125" customWidth="1"/>
     <col min="3" max="3" width="76.81640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1443,18 +1508,18 @@
         <v>11</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>84</v>
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>90</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -1466,10 +1531,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">

--- a/src/main/resources/ScanTestData.xlsx
+++ b/src/main/resources/ScanTestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation Setup\AST Automation\Automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9181A05E-BC8A-4E17-A1DC-1F4DD2E430C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A3EBF7-9C23-4199-BE03-34B71218082C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScanSheet" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="90">
   <si>
     <t>ScenarioDescription</t>
   </si>
@@ -304,9 +304,6 @@
   </si>
   <si>
     <t>KICS scan with empty Platform</t>
-  </si>
-  <si>
-    <t>`--iac-security-platforms Invalid_platform</t>
   </si>
 </sst>
 </file>
@@ -1511,29 +1508,6 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-    </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C15" s="3"/>
     </row>

--- a/src/main/resources/ScanTestData.xlsx
+++ b/src/main/resources/ScanTestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation Setup\AST Automation\Automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A3EBF7-9C23-4199-BE03-34B71218082C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC36A62C-2BC5-4B5D-B6C4-9337B7067573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScanSheet" sheetId="1" r:id="rId1"/>
@@ -926,9 +926,6 @@
       <c r="G11" t="s">
         <v>22</v>
       </c>
-      <c r="H11" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -949,6 +946,9 @@
       <c r="G12" t="s">
         <v>8</v>
       </c>
+      <c r="H12" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -972,9 +972,6 @@
       <c r="G13" t="s">
         <v>8</v>
       </c>
-      <c r="H13" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
@@ -998,6 +995,9 @@
       <c r="G14" t="s">
         <v>8</v>
       </c>
+      <c r="H14" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -1021,9 +1021,6 @@
       <c r="G15" t="s">
         <v>8</v>
       </c>
-      <c r="H15" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -1047,6 +1044,9 @@
       <c r="G16" t="s">
         <v>8</v>
       </c>
+      <c r="H16" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
@@ -1093,9 +1093,6 @@
       <c r="G18" t="s">
         <v>8</v>
       </c>
-      <c r="H18" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
@@ -1145,6 +1142,9 @@
       <c r="G20" t="s">
         <v>8</v>
       </c>
+      <c r="H20" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
@@ -1214,9 +1214,6 @@
       <c r="G23" t="s">
         <v>8</v>
       </c>
-      <c r="H23" t="s">
-        <v>47</v>
-      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
@@ -1241,7 +1238,7 @@
         <v>8</v>
       </c>
       <c r="H24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -1267,7 +1264,7 @@
         <v>8</v>
       </c>
       <c r="H25" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -1292,6 +1289,9 @@
       <c r="G26" t="s">
         <v>8</v>
       </c>
+      <c r="H26" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
@@ -1315,9 +1315,6 @@
       <c r="G27" t="s">
         <v>8</v>
       </c>
-      <c r="H27" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
@@ -1341,6 +1338,9 @@
       <c r="G28" t="s">
         <v>8</v>
       </c>
+      <c r="H28" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
@@ -1364,9 +1364,6 @@
       <c r="G29" t="s">
         <v>8</v>
       </c>
-      <c r="H29" t="s">
-        <v>65</v>
-      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
@@ -1391,7 +1388,7 @@
         <v>8</v>
       </c>
       <c r="H30" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -1416,6 +1413,9 @@
       <c r="G31" t="s">
         <v>8</v>
       </c>
+      <c r="H31" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
@@ -1439,11 +1439,8 @@
       <c r="G32" t="s">
         <v>8</v>
       </c>
-      <c r="H32" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>73</v>
       </c>
@@ -1464,6 +1461,9 @@
       </c>
       <c r="G33" t="s">
         <v>8</v>
+      </c>
+      <c r="H33" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/ScanTestData.xlsx
+++ b/src/main/resources/ScanTestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation Setup\AST Automation\Automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A3EBF7-9C23-4199-BE03-34B71218082C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD84E8E-E8EF-4081-9335-854C4AFB1B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScanSheet" sheetId="1" r:id="rId1"/>
@@ -926,9 +926,6 @@
       <c r="G11" t="s">
         <v>22</v>
       </c>
-      <c r="H11" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -949,6 +946,9 @@
       <c r="G12" t="s">
         <v>8</v>
       </c>
+      <c r="H12" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -972,9 +972,6 @@
       <c r="G13" t="s">
         <v>8</v>
       </c>
-      <c r="H13" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
@@ -998,6 +995,9 @@
       <c r="G14" t="s">
         <v>8</v>
       </c>
+      <c r="H14" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -1021,9 +1021,6 @@
       <c r="G15" t="s">
         <v>8</v>
       </c>
-      <c r="H15" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -1047,6 +1044,9 @@
       <c r="G16" t="s">
         <v>8</v>
       </c>
+      <c r="H16" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
@@ -1093,9 +1093,6 @@
       <c r="G18" t="s">
         <v>8</v>
       </c>
-      <c r="H18" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
@@ -1145,6 +1142,9 @@
       <c r="G20" t="s">
         <v>8</v>
       </c>
+      <c r="H20" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
@@ -1214,9 +1214,6 @@
       <c r="G23" t="s">
         <v>8</v>
       </c>
-      <c r="H23" t="s">
-        <v>47</v>
-      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
@@ -1241,7 +1238,7 @@
         <v>8</v>
       </c>
       <c r="H24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -1267,7 +1264,7 @@
         <v>8</v>
       </c>
       <c r="H25" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -1292,6 +1289,9 @@
       <c r="G26" t="s">
         <v>8</v>
       </c>
+      <c r="H26" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
@@ -1315,9 +1315,6 @@
       <c r="G27" t="s">
         <v>8</v>
       </c>
-      <c r="H27" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
@@ -1341,6 +1338,9 @@
       <c r="G28" t="s">
         <v>8</v>
       </c>
+      <c r="H28" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
@@ -1364,9 +1364,6 @@
       <c r="G29" t="s">
         <v>8</v>
       </c>
-      <c r="H29" t="s">
-        <v>65</v>
-      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
@@ -1391,7 +1388,7 @@
         <v>8</v>
       </c>
       <c r="H30" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -1416,6 +1413,9 @@
       <c r="G31" t="s">
         <v>8</v>
       </c>
+      <c r="H31" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
@@ -1439,11 +1439,8 @@
       <c r="G32" t="s">
         <v>8</v>
       </c>
-      <c r="H32" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>73</v>
       </c>
@@ -1464,6 +1461,9 @@
       </c>
       <c r="G33" t="s">
         <v>8</v>
+      </c>
+      <c r="H33" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/ScanTestData.xlsx
+++ b/src/main/resources/ScanTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation Setup\AST Automation\Automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD84E8E-E8EF-4081-9335-854C4AFB1B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1A5044-1B29-49AE-99C6-9B9E5D6AF945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="93">
   <si>
     <t>ScenarioDescription</t>
   </si>
@@ -304,6 +304,15 @@
   </si>
   <si>
     <t>KICS scan with empty Platform</t>
+  </si>
+  <si>
+    <t>SCA scan with valid Sca Resolver Path with Zip Source</t>
+  </si>
+  <si>
+    <t>`--sca-resolver src/main/resources/ScaResolver-win64/ScaResolver.exe</t>
+  </si>
+  <si>
+    <t>Scanning Zip files is not supported by ScaResolver.Please use non-zip source</t>
   </si>
 </sst>
 </file>
@@ -676,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.90625" customWidth="1"/>
@@ -1464,6 +1473,32 @@
       </c>
       <c r="H33" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
